--- a/Corpus/descriptive_analysis/ISO_3166_country_codes.xlsx
+++ b/Corpus/descriptive_analysis/ISO_3166_country_codes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/poppyriddle/Documents/Github/IPCC_corpus/Corpus/descriptive_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1636F907-5FE9-4E49-8659-CDE42A076A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D16514-4A73-E646-A57B-A41D81E7BEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16940" xr2:uid="{ED9D70EB-6E39-434E-8929-F7D8A7844212}"/>
   </bookViews>
